--- a/cviky-sablona.xlsx
+++ b/cviky-sablona.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,8 +81,12 @@
       <i val="1"/>
       <color rgb="00555555"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +103,11 @@
         <fgColor rgb="00FFF7E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F7A45"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -112,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -147,6 +156,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -512,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -543,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -724,7 +738,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
@@ -737,7 +750,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -754,6 +766,64 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>(vrátane príkladu — po zmazaní príkladu odpočítaj 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NOVÉ: každý cvik musí mať vyplnené aj Prečo, Rozostavenie, Podmienky, Sťaženie,</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Zjednodušenie a Dávkovanie — bez nich sa cvik do appky nenahrá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Prečo = jedna veta, čo sa tým prenáša do zápasu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Podmienky = pravidlo, ktoré hráča núti robiť tému (napr. „prvý dotyk musí ísť dopredu“).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sťaženie / Zjednodušenie = ako cvik upraviť pre lepších a slabších.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dávkovanie = počet opakovaní alebo série a pauzy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Postup:  python3 scripts/excel_to_json.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         python3 scripts/build_db.py &amp;&amp; python3 scripts/inject.py</t>
         </is>
       </c>
     </row>
@@ -768,193 +838,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q501"/>
+  <dimension ref="A1:V501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
     <col width="42" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Názov cviku</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Názov</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Časť</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>Zručnosť (hlavná)</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>Ďalšie zručnosti (čiarkou)</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>Téma (voliteľné)</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>Zručnosť</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>Ďalšie zručnosti</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>Téma</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Vek od</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Vek do</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
-        <is>
-          <t>Počet hráčov</t>
-        </is>
-      </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>Hráči</t>
+        </is>
+      </c>
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Priestor</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Intenzita</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
-        <is>
-          <t>Trvanie (min)</t>
-        </is>
-      </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
+        <is>
+          <t>Minúty</t>
+        </is>
+      </c>
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Pomôcky</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
-        <is>
-          <t>Popis / priebeh</t>
-        </is>
-      </c>
-      <c r="O1" s="8" t="inlineStr">
-        <is>
-          <t>Na čo dbať (coaching points)</t>
-        </is>
-      </c>
-      <c r="P1" s="8" t="inlineStr">
-        <is>
-          <t>Nákres (odkaz/obrázok)</t>
-        </is>
-      </c>
-      <c r="Q1" s="8" t="inlineStr">
-        <is>
-          <t>Video (odkaz)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>Slalom s loptou na rýchlosť</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
+        <is>
+          <t>Prečo</t>
+        </is>
+      </c>
+      <c r="O1" s="16" t="inlineStr">
+        <is>
+          <t>Rozostavenie</t>
+        </is>
+      </c>
+      <c r="P1" s="16" t="inlineStr">
+        <is>
+          <t>Priebeh</t>
+        </is>
+      </c>
+      <c r="Q1" s="16" t="inlineStr">
+        <is>
+          <t>Podmienky</t>
+        </is>
+      </c>
+      <c r="R1" s="16" t="inlineStr">
+        <is>
+          <t>Sťaženie</t>
+        </is>
+      </c>
+      <c r="S1" s="16" t="inlineStr">
+        <is>
+          <t>Zjednodušenie</t>
+        </is>
+      </c>
+      <c r="T1" s="16" t="inlineStr">
+        <is>
+          <t>Na čo dbať</t>
+        </is>
+      </c>
+      <c r="U1" s="16" t="inlineStr">
+        <is>
+          <t>Dávkovanie</t>
+        </is>
+      </c>
+      <c r="V1" s="16" t="inlineStr">
+        <is>
+          <t>Úroveň</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>X001</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Slalom s prekonaním strážcu</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>PČ</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Vedenie lopty priamym priehlavkom vo voľnom priestore</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Zmeny rýchlosti pri vedení lopty</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>Rýchlym vedením lopty</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>U11</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
-        <is>
-          <t>Stredný priestor</t>
-        </is>
-      </c>
-      <c r="K2" s="9" t="inlineStr">
-        <is>
-          <t>Stredná</t>
-        </is>
-      </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>8–14</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>24×18 m</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>stredná</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
-        <is>
-          <t>6 kužeľov, lopty pre každého</t>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>méty, lopta pre každého</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>Hráči vedú loptu slalomom medzi kužeľmi, po poslednom šprint s loptou do cieľovej zóny. 2 rady, súťaž.</t>
+          <t>V zápase sa hráč dostáva do súboja v rýchlosti, nie zo státia — preto vedenie a prekonanie spájame do jednej akcie.</t>
         </is>
       </c>
       <c r="O2" s="10" t="inlineStr">
         <is>
-          <t>Nízke ťažisko, lopta blízko nohy, po prekážke zrýchliť, hlava hore.</t>
-        </is>
-      </c>
-      <c r="P2" s="9" t="inlineStr"/>
-      <c r="Q2" s="9" t="inlineStr"/>
+          <t>Rad kužeľov na 15 m, za posledným stojí obranca a dve brány z mét.</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>Hráč prejde slalom priamym priehlavkom, po poslednom kuželi zrýchli a rieši 1v1 proti obrancovi. Prejde ľubovoľnou bránou.</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>Posledné tri metre pred obrancom musia byť v maximálnej rýchlosti — bez spomalenia.</t>
+        </is>
+      </c>
+      <c r="R2" s="17" t="inlineStr">
+        <is>
+          <t>Obranca bráni naplno. / Časový limit šesť sekúnd na celú akciu.</t>
+        </is>
+      </c>
+      <c r="S2" s="17" t="inlineStr">
+        <is>
+          <t>Obranca sa pohybuje len bokom a neodoberá.</t>
+        </is>
+      </c>
+      <c r="T2" s="17" t="inlineStr">
+        <is>
+          <t>Lopta blízko nohy v slalome, ďalej od nohy po ňom. Hlava hore pred posledným kuželom. Po prekonaní hneď zrýchli.</t>
+        </is>
+      </c>
+      <c r="U2" s="17" t="inlineStr">
+        <is>
+          <t>8–10 opakovaní, pomer práca:pauza 1:4</t>
+        </is>
+      </c>
+      <c r="V2" s="17" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n"/>
@@ -10438,7 +10571,7 @@
       <c r="Q501" s="11" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyber hodnotu zo zoznamu." promptTitle="Vyber zo zoznamu" prompt="PČ / HČ / ZČ" type="list">
       <formula1>=Zoznamy!$A$2:$A$4</formula1>
     </dataValidation>
@@ -10460,6 +10593,9 @@
     <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Neplatná hodnota" error="Vyber hodnotu zo zoznamu." promptTitle="Vyber zo zoznamu" prompt="Nízka / Stredná / Vysoká" type="list">
       <formula1>=Zoznamy!$F$2:$F$4</formula1>
     </dataValidation>
+    <dataValidation sqref="V2:V500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Zoznamy!$G$2:$G$4</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10471,7 +10607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10513,6 +10649,11 @@
           <t>Intenzita</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Úroveň</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
@@ -10545,6 +10686,11 @@
           <t>Nízka</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>foundation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -10577,6 +10723,11 @@
           <t>Stredná</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -10607,6 +10758,11 @@
       <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Vysoká</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>pro</t>
         </is>
       </c>
     </row>
